--- a/Tables/CAAR_grouped.xlsx
+++ b/Tables/CAAR_grouped.xlsx
@@ -480,25 +480,25 @@
         <v>5.052851658658023</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0338</v>
+        <v>0.0321</v>
       </c>
       <c r="D2" t="n">
         <v>3.667594918876807</v>
       </c>
       <c r="E2" t="n">
-        <v>0.102</v>
+        <v>0.1006</v>
       </c>
       <c r="F2" t="n">
         <v>4.675722190972281</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0459</v>
+        <v>0.0433</v>
       </c>
       <c r="H2" t="n">
         <v>9.074995971892251</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0013</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="3">
@@ -511,7 +511,7 @@
         <v>-4.092188627994692</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0111</v>
+        <v>0.0107</v>
       </c>
       <c r="D3" t="n">
         <v>-5.727892301048808</v>
@@ -542,25 +542,25 @@
         <v>-0.1369062728111365</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9169</v>
+        <v>0.9166</v>
       </c>
       <c r="D4" t="n">
         <v>0.3134657556244456</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8117</v>
+        <v>0.8126</v>
       </c>
       <c r="F4" t="n">
         <v>-2.358213530816478</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0767</v>
+        <v>0.0743</v>
       </c>
       <c r="H4" t="n">
         <v>-0.767438907507649</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5641</v>
+        <v>0.5616</v>
       </c>
     </row>
     <row r="5">
@@ -573,25 +573,25 @@
         <v>9.145040286652716</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0112</v>
+        <v>0.0098</v>
       </c>
       <c r="D5" t="n">
         <v>9.395487219925615</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0052</v>
+        <v>0.0043</v>
       </c>
       <c r="F5" t="n">
         <v>10.54250952846779</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0046</v>
+        <v>0.0039</v>
       </c>
       <c r="H5" t="n">
         <v>18.94563165346447</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -604,13 +604,13 @@
         <v>5.18975793146916</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0415</v>
+        <v>0.0412</v>
       </c>
       <c r="D6" t="n">
         <v>3.354129163252362</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0936</v>
       </c>
       <c r="F6" t="n">
         <v>7.03393572178876</v>
@@ -622,7 +622,7 @@
         <v>9.842434879399901</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0035</v>
+        <v>0.0039</v>
       </c>
     </row>
     <row r="7">
@@ -635,25 +635,25 @@
         <v>-3.955282355183555</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0641</v>
+        <v>0.0582</v>
       </c>
       <c r="D7" t="n">
         <v>-6.041358056673253</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0013</v>
+        <v>0.0024</v>
       </c>
       <c r="F7" t="n">
         <v>-3.508573806679033</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0956</v>
       </c>
       <c r="H7" t="n">
         <v>-9.103196774064564</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0017</v>
+        <v>0.0012</v>
       </c>
     </row>
   </sheetData>
